--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-05-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-05-2025.xlsx
@@ -538,12 +538,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.98</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.98</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>£12.31</t>
+          <t>£11.17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -635,42 +635,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>£13.15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>£13.15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£12.83</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>£14.00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>£13.28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>£13.15</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>£13.33</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>£13.33</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>£12.83</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>£14.00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>£13.28</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>£13.15</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>£13.33</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>£14.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -732,24 +732,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>£16.73</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>£16.73</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>£14.46</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>£17.00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>£17.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>£14.46</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£17.00</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>£16.83</t>
@@ -767,7 +767,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>£17.04</t>
+          <t>£16.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -829,34 +829,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>£17.48</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>£17.48</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£16.74</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>£17.50</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>£17.93</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>£17.50</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>£16.74</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£17.50</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£17.93</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£17.50</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>£17.48</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>£18.58</t>
+          <t>£16.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -926,24 +926,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>£21.65</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>£21.65</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£21.44</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>£22.00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>£22.00</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>£21.44</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>£22.00</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>£21.92</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>£23.64</t>
+          <t>£21.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£24.60</t>
+          <t>£23.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£24.60</t>
+          <t>£23.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>£25.29</t>
+          <t>£23.15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1120,24 +1120,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>£23.86</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>£23.86</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>£23.49</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>£24.00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>£24.00</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>£23.49</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>£24.00</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>£24.17</t>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>£25.84</t>
+          <t>£23.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1217,29 +1217,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>£26.87</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>£26.87</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>£26.78</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>£27.00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>£27.00</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>£26.78</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>£27.00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>£27.00</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>£26.87</t>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>£29.69</t>
+          <t>£26.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1314,24 +1314,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>£29.36</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£29.36</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£29.31</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>£30.50</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>£30.50</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£29.31</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£30.50</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>£29.50</t>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>£31.89</t>
+          <t>£29.33</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1411,24 +1411,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>£29.42</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>£29.42</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>£28.60</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>£29.50</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>£29.50</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>£28.60</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>£29.50</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>£30.42</t>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>£28.96</t>
+          <t>£28.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£37.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£37.00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1605,42 +1605,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>£35.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£35.90</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£35.08</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>£37.50</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£36.46</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>£35.90</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>£38.00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>£35.08</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£36.46</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>£38.00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>£38.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>£44.50</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>£44.50</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£48.12</t>
+          <t>£44.64</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£48.12</t>
+          <t>£44.64</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>£49.16</t>
+          <t>£43.58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£33.20</t>
+          <t>£31.90</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£33.20</t>
+          <t>£31.90</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£45.89</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£45.89</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>£1287.36</t>
+          <t>£1172.16</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
